--- a/database/event/6864/event_6864_evp_summary.xlsx
+++ b/database/event/6864/event_6864_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.2149</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4.1678</v>
       </c>
       <c r="D2" t="n">
         <v>3.3013</v>
@@ -545,7 +545,7 @@
         <v>6.1246</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.7701</v>
       </c>
       <c r="D3" t="n">
         <v>2.0528</v>
@@ -591,7 +591,7 @@
         <v>5.7608</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.6056</v>
       </c>
       <c r="D4" t="n">
         <v>1.9059</v>
@@ -637,7 +637,7 @@
         <v>5.7453</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.5985</v>
       </c>
       <c r="D5" t="n">
         <v>1.8996</v>
@@ -683,7 +683,7 @@
         <v>5.4071</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.4456</v>
       </c>
       <c r="D6" t="n">
         <v>1.763</v>
@@ -729,7 +729,7 @@
         <v>4.7523</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.1494</v>
       </c>
       <c r="D7" t="n">
         <v>1.4985</v>
@@ -775,7 +775,7 @@
         <v>3.9736</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.7972</v>
       </c>
       <c r="D8" t="n">
         <v>1.1839</v>
@@ -821,7 +821,7 @@
         <v>3.9483</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.7858</v>
       </c>
       <c r="D9" t="n">
         <v>1.1737</v>
@@ -867,7 +867,7 @@
         <v>3.7818</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.7105</v>
       </c>
       <c r="D10" t="n">
         <v>1.1064</v>
@@ -913,7 +913,7 @@
         <v>3.4081</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.5415</v>
       </c>
       <c r="D11" t="n">
         <v>0.9554</v>
@@ -959,7 +959,7 @@
         <v>3.2635</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.4761</v>
       </c>
       <c r="D12" t="n">
         <v>0.897</v>
@@ -1005,7 +1005,7 @@
         <v>2.7218</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="D13" t="n">
         <v>0.6782</v>
@@ -1051,7 +1051,7 @@
         <v>2.6211</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.1855</v>
       </c>
       <c r="D14" t="n">
         <v>0.6375</v>
@@ -1097,7 +1097,7 @@
         <v>2.5159</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.1379</v>
       </c>
       <c r="D15" t="n">
         <v>0.595</v>
@@ -1143,7 +1143,7 @@
         <v>2.5077</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.1342</v>
       </c>
       <c r="D16" t="n">
         <v>0.5917</v>
@@ -1189,7 +1189,7 @@
         <v>2.4769</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.1203</v>
       </c>
       <c r="D17" t="n">
         <v>0.5793</v>
@@ -1235,7 +1235,7 @@
         <v>1.9304</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.8731</v>
       </c>
       <c r="D18" t="n">
         <v>0.3585</v>
@@ -1281,7 +1281,7 @@
         <v>1.7728</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.8018</v>
       </c>
       <c r="D19" t="n">
         <v>0.2948</v>
@@ -1327,7 +1327,7 @@
         <v>1.7634</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.7976</v>
       </c>
       <c r="D20" t="n">
         <v>0.291</v>
@@ -1373,7 +1373,7 @@
         <v>1.7206</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.7782</v>
       </c>
       <c r="D21" t="n">
         <v>0.2737</v>
@@ -1419,7 +1419,7 @@
         <v>1.6368</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.7403</v>
       </c>
       <c r="D22" t="n">
         <v>0.2399</v>
@@ -1465,7 +1465,7 @@
         <v>1.3284</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.6008</v>
       </c>
       <c r="D23" t="n">
         <v>0.1153</v>
@@ -1511,7 +1511,7 @@
         <v>1.2422</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.5618</v>
       </c>
       <c r="D24" t="n">
         <v>0.0805</v>
@@ -1557,7 +1557,7 @@
         <v>1.1575</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.5235</v>
       </c>
       <c r="D25" t="n">
         <v>0.0462</v>
@@ -1603,7 +1603,7 @@
         <v>1.0646</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.4815</v>
       </c>
       <c r="D26" t="n">
         <v>0.008699999999999999</v>
@@ -1649,7 +1649,7 @@
         <v>1.0546</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="D27" t="n">
         <v>0.0047</v>
@@ -1695,7 +1695,7 @@
         <v>1.0047</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.4544</v>
       </c>
       <c r="D28" t="n">
         <v>-0.0155</v>
@@ -1741,7 +1741,7 @@
         <v>0.9056</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.4096</v>
       </c>
       <c r="D29" t="n">
         <v>-0.0555</v>
@@ -1787,7 +1787,7 @@
         <v>0.74</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.3347</v>
       </c>
       <c r="D30" t="n">
         <v>-0.1224</v>
@@ -1833,7 +1833,7 @@
         <v>0.7361</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="D31" t="n">
         <v>-0.124</v>
@@ -1879,7 +1879,7 @@
         <v>0.6957</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.3147</v>
       </c>
       <c r="D32" t="n">
         <v>-0.1403</v>
@@ -1925,7 +1925,7 @@
         <v>0.6758</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.3057</v>
       </c>
       <c r="D33" t="n">
         <v>-0.1484</v>
@@ -1971,7 +1971,7 @@
         <v>0.5814</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="D34" t="n">
         <v>-0.1865</v>
@@ -2017,7 +2017,7 @@
         <v>0.5803</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2625</v>
       </c>
       <c r="D35" t="n">
         <v>-0.1869</v>
@@ -2063,7 +2063,7 @@
         <v>0.5743</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.2598</v>
       </c>
       <c r="D36" t="n">
         <v>-0.1894</v>
@@ -2109,7 +2109,7 @@
         <v>0.4914</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.2223</v>
       </c>
       <c r="D37" t="n">
         <v>-0.2228</v>
@@ -2155,7 +2155,7 @@
         <v>0.4821</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="D38" t="n">
         <v>-0.2266</v>
@@ -2201,7 +2201,7 @@
         <v>0.3621</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.1638</v>
       </c>
       <c r="D39" t="n">
         <v>-0.2751</v>
@@ -2247,7 +2247,7 @@
         <v>0.3234</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.1463</v>
       </c>
       <c r="D40" t="n">
         <v>-0.2907</v>
@@ -2293,7 +2293,7 @@
         <v>0.3169</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.1433</v>
       </c>
       <c r="D41" t="n">
         <v>-0.2933</v>
@@ -2339,7 +2339,7 @@
         <v>0.2748</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.1243</v>
       </c>
       <c r="D42" t="n">
         <v>-0.3103</v>
@@ -2385,7 +2385,7 @@
         <v>0.188</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D43" t="n">
         <v>-0.3454</v>
@@ -2431,7 +2431,7 @@
         <v>0.1853</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.0838</v>
       </c>
       <c r="D44" t="n">
         <v>-0.3465</v>
@@ -2477,7 +2477,7 @@
         <v>0.1517</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="D45" t="n">
         <v>-0.3601</v>
@@ -2523,7 +2523,7 @@
         <v>0.0917</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3843</v>
@@ -2569,7 +2569,7 @@
         <v>0.0717</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.0324</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3924</v>
@@ -2615,7 +2615,7 @@
         <v>0.0066</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D48" t="n">
         <v>-0.4187</v>
@@ -2661,7 +2661,7 @@
         <v>-0.1694</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.0766</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4898</v>
@@ -2707,7 +2707,7 @@
         <v>-0.1822</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.0824</v>
       </c>
       <c r="D50" t="n">
         <v>-0.495</v>
@@ -2753,7 +2753,7 @@
         <v>-0.2689</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.1216</v>
       </c>
       <c r="D51" t="n">
         <v>-0.53</v>
@@ -2799,7 +2799,7 @@
         <v>-0.271</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.1226</v>
       </c>
       <c r="D52" t="n">
         <v>-0.5308</v>
@@ -2845,7 +2845,7 @@
         <v>-0.3239</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1465</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5522</v>
@@ -2891,7 +2891,7 @@
         <v>-0.3325</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1504</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5557</v>
@@ -2937,7 +2937,7 @@
         <v>-0.3751</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1697</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5729</v>
@@ -2983,7 +2983,7 @@
         <v>-0.4281</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1936</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5943000000000001</v>
@@ -3029,7 +3029,7 @@
         <v>-0.5321</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.2407</v>
       </c>
       <c r="D57" t="n">
         <v>-0.6363</v>
@@ -3075,7 +3075,7 @@
         <v>-0.5462</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.247</v>
       </c>
       <c r="D58" t="n">
         <v>-0.642</v>
@@ -3121,7 +3121,7 @@
         <v>-0.6458</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2921</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6823</v>
@@ -3167,7 +3167,7 @@
         <v>-0.6698</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.3029</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6919</v>
@@ -3213,7 +3213,7 @@
         <v>-0.7054</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.319</v>
       </c>
       <c r="D61" t="n">
         <v>-0.7063</v>
@@ -3259,7 +3259,7 @@
         <v>-0.7374000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3335</v>
       </c>
       <c r="D62" t="n">
         <v>-0.7193000000000001</v>
@@ -3305,7 +3305,7 @@
         <v>-0.7548</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.3414</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7262999999999999</v>
@@ -3351,7 +3351,7 @@
         <v>-0.785</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.355</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7385</v>
@@ -3397,7 +3397,7 @@
         <v>-0.7959000000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.36</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7429</v>
@@ -3443,7 +3443,7 @@
         <v>-0.7999000000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.3618</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7445000000000001</v>
@@ -3489,7 +3489,7 @@
         <v>-0.8314</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.376</v>
       </c>
       <c r="D67" t="n">
         <v>-0.7572</v>
@@ -3535,7 +3535,7 @@
         <v>-0.8667</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.392</v>
       </c>
       <c r="D68" t="n">
         <v>-0.7715</v>
@@ -3581,7 +3581,7 @@
         <v>-0.9275</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.4195</v>
       </c>
       <c r="D69" t="n">
         <v>-0.7961</v>
@@ -3627,7 +3627,7 @@
         <v>-1.0309</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.4663</v>
       </c>
       <c r="D70" t="n">
         <v>-0.8378</v>
@@ -3673,7 +3673,7 @@
         <v>-1.2095</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.547</v>
       </c>
       <c r="D71" t="n">
         <v>-0.91</v>
@@ -3719,7 +3719,7 @@
         <v>-1.2832</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.5804</v>
       </c>
       <c r="D72" t="n">
         <v>-0.9397</v>
@@ -3765,7 +3765,7 @@
         <v>-1.3168</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.5956</v>
       </c>
       <c r="D73" t="n">
         <v>-0.9533</v>
@@ -3811,7 +3811,7 @@
         <v>-1.4449</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.6535</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0051</v>
@@ -3857,7 +3857,7 @@
         <v>-1.5348</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.6942</v>
       </c>
       <c r="D75" t="n">
         <v>-1.0414</v>
@@ -3903,7 +3903,7 @@
         <v>-1.5481</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.7002</v>
       </c>
       <c r="D76" t="n">
         <v>-1.0468</v>
@@ -3949,7 +3949,7 @@
         <v>-1.7401</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-0.787</v>
       </c>
       <c r="D77" t="n">
         <v>-1.1243</v>
@@ -3995,7 +3995,7 @@
         <v>-1.8445</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-0.8343</v>
       </c>
       <c r="D78" t="n">
         <v>-1.1665</v>
@@ -4041,7 +4041,7 @@
         <v>-2.4349</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.1013</v>
       </c>
       <c r="D79" t="n">
         <v>-1.405</v>
@@ -4087,7 +4087,7 @@
         <v>-3.0685</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.3879</v>
       </c>
       <c r="D80" t="n">
         <v>-1.661</v>
@@ -4133,7 +4133,7 @@
         <v>-3.7655</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-1.7031</v>
       </c>
       <c r="D81" t="n">
         <v>-1.9425</v>
@@ -4179,7 +4179,7 @@
         <v>-3.9504</v>
       </c>
       <c r="C82" t="n">
-        <v>-0</v>
+        <v>-1.7867</v>
       </c>
       <c r="D82" t="n">
         <v>-2.0172</v>

--- a/database/event/6864/event_6864_evp_summary.xlsx
+++ b/database/event/6864/event_6864_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.2149</v>
+        <v>9.183199999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1678</v>
+        <v>4.1535</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3013</v>
+        <v>3.2147</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2149</v>
+        <v>9.183199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3109</v>
+        <v>4.2792</v>
       </c>
       <c r="G2" t="n">
         <v>4.904</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4565</v>
+        <v>4.4068</v>
       </c>
       <c r="I2" t="n">
         <v>4.519</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1246</v>
+        <v>6.1941</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7701</v>
+        <v>2.8015</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0528</v>
+        <v>2.0238</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1246</v>
+        <v>6.1941</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1768</v>
+        <v>4.2463</v>
       </c>
       <c r="G3" t="n">
         <v>1.9478</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2437</v>
+        <v>4.5232</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4396</v>
+        <v>3.6661</v>
       </c>
       <c r="J3" t="n">
         <v>1.9478</v>
@@ -575,7 +575,7 @@
         <v>82</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3874</v>
+        <v>5.6139</v>
       </c>
       <c r="N3" t="n">
         <v>255</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7608</v>
+        <v>5.7217</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6056</v>
+        <v>2.5879</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9059</v>
+        <v>1.8356</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7608</v>
+        <v>5.7217</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5097</v>
+        <v>3.4706</v>
       </c>
       <c r="G4" t="n">
         <v>2.2511</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5097</v>
+        <v>3.4706</v>
       </c>
       <c r="I4" t="n">
         <v>3.559</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7453</v>
+        <v>5.7101</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5985</v>
+        <v>2.5826</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8996</v>
+        <v>1.831</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7453</v>
+        <v>5.7101</v>
       </c>
       <c r="F5" t="n">
-        <v>4.625</v>
+        <v>4.5898</v>
       </c>
       <c r="G5" t="n">
         <v>1.1203</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9489</v>
+        <v>4.8937</v>
       </c>
       <c r="I5" t="n">
         <v>5.0183</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4071</v>
+        <v>5.4464</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4456</v>
+        <v>2.4634</v>
       </c>
       <c r="D6" t="n">
-        <v>1.763</v>
+        <v>1.7259</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4071</v>
+        <v>5.4464</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1137</v>
+        <v>3.153</v>
       </c>
       <c r="G6" t="n">
         <v>2.2934</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1137</v>
+        <v>3.153</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1428</v>
+        <v>3.2063</v>
       </c>
       <c r="J6" t="n">
         <v>2.2934</v>
@@ -713,7 +713,7 @@
         <v>214</v>
       </c>
       <c r="M6" t="n">
-        <v>5.436199999999999</v>
+        <v>5.499700000000001</v>
       </c>
       <c r="N6" t="n">
         <v>438</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7523</v>
+        <v>4.7783</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1494</v>
+        <v>2.1612</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4985</v>
+        <v>1.4598</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7523</v>
+        <v>4.7783</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2934</v>
+        <v>4.3194</v>
       </c>
       <c r="G7" t="n">
         <v>0.4589</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7127</v>
+        <v>4.8175</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8198</v>
+        <v>3.9047</v>
       </c>
       <c r="J7" t="n">
         <v>0.4589</v>
@@ -759,7 +759,7 @@
         <v>72</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2787</v>
+        <v>4.3636</v>
       </c>
       <c r="N7" t="n">
         <v>218</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9736</v>
+        <v>4.0218</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7972</v>
+        <v>1.819</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1839</v>
+        <v>1.1584</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9736</v>
+        <v>4.0218</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8456</v>
+        <v>4.3326</v>
       </c>
       <c r="G8" t="n">
-        <v>1.128</v>
+        <v>-0.3108</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8456</v>
+        <v>4.8707</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8721</v>
+        <v>3.9478</v>
       </c>
       <c r="J8" t="n">
-        <v>1.128</v>
+        <v>-0.3108</v>
       </c>
       <c r="K8" t="n">
-        <v>233</v>
+        <v>146</v>
       </c>
       <c r="L8" t="n">
-        <v>214</v>
+        <v>72</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0001</v>
+        <v>3.637</v>
       </c>
       <c r="N8" t="n">
-        <v>447</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9483</v>
+        <v>3.9524</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7858</v>
+        <v>1.7876</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1737</v>
+        <v>1.1307</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9483</v>
+        <v>3.9524</v>
       </c>
       <c r="F9" t="n">
-        <v>4.2591</v>
+        <v>2.8244</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3108</v>
+        <v>1.128</v>
       </c>
       <c r="H9" t="n">
-        <v>4.575</v>
+        <v>2.8244</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7082</v>
+        <v>2.8721</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3108</v>
+        <v>1.128</v>
       </c>
       <c r="K9" t="n">
-        <v>146</v>
+        <v>233</v>
       </c>
       <c r="L9" t="n">
-        <v>72</v>
+        <v>214</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3974</v>
+        <v>4.0001</v>
       </c>
       <c r="N9" t="n">
-        <v>218</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10">
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7818</v>
+        <v>3.7665</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7105</v>
+        <v>1.7036</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1064</v>
+        <v>1.0567</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7818</v>
+        <v>3.7665</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3708</v>
+        <v>1.3555</v>
       </c>
       <c r="G10" t="n">
         <v>2.411</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3708</v>
+        <v>1.3555</v>
       </c>
       <c r="I10" t="n">
         <v>1.39</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4081</v>
+        <v>3.4002</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5415</v>
+        <v>1.5379</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9554</v>
+        <v>0.9107</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4081</v>
+        <v>3.4002</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1003</v>
+        <v>2.0924</v>
       </c>
       <c r="G11" t="n">
         <v>1.3078</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1003</v>
+        <v>2.0924</v>
       </c>
       <c r="I11" t="n">
         <v>2.11</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2635</v>
+        <v>3.2538</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4761</v>
+        <v>1.4717</v>
       </c>
       <c r="D12" t="n">
-        <v>0.897</v>
+        <v>0.8524</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2635</v>
+        <v>3.2538</v>
       </c>
       <c r="F12" t="n">
-        <v>2.594</v>
+        <v>2.5843</v>
       </c>
       <c r="G12" t="n">
         <v>0.6695</v>
       </c>
       <c r="H12" t="n">
-        <v>2.594</v>
+        <v>2.5843</v>
       </c>
       <c r="I12" t="n">
         <v>2.6061</v>
@@ -998,323 +998,323 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7218</v>
+        <v>2.8452</v>
       </c>
       <c r="C13" t="n">
-        <v>1.231</v>
+        <v>1.2869</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6782</v>
+        <v>0.6896</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7218</v>
+        <v>2.8452</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7218</v>
+        <v>2.8452</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7218</v>
+        <v>2.8452</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7345</v>
+        <v>2.8452</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7345</v>
+        <v>2.8452</v>
       </c>
       <c r="N13" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6211</v>
+        <v>2.7123</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1855</v>
+        <v>1.2267</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6375</v>
+        <v>0.6367</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6211</v>
+        <v>2.7123</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6211</v>
+        <v>2.7123</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6211</v>
+        <v>2.7123</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6211</v>
+        <v>2.7351</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6211</v>
+        <v>2.7351</v>
       </c>
       <c r="N14" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5159</v>
+        <v>2.6974</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1379</v>
+        <v>1.22</v>
       </c>
       <c r="D15" t="n">
-        <v>0.595</v>
+        <v>0.6307</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5159</v>
+        <v>2.6974</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2156</v>
+        <v>2.6974</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3003</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2156</v>
+        <v>2.6974</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2363</v>
+        <v>2.6974</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3003</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="L15" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5366</v>
+        <v>2.6974</v>
       </c>
       <c r="N15" t="n">
-        <v>407</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5077</v>
+        <v>2.6211</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1342</v>
+        <v>1.1855</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5917</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5077</v>
+        <v>2.6211</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5077</v>
+        <v>2.6211</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5077</v>
+        <v>2.6211</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5077</v>
+        <v>2.6211</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>209</v>
+        <v>149</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5077</v>
+        <v>2.6211</v>
       </c>
       <c r="N16" t="n">
-        <v>209</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4769</v>
+        <v>2.4994</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1203</v>
+        <v>1.1305</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5793</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4769</v>
+        <v>2.4994</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4769</v>
+        <v>2.1991</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.3003</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4769</v>
+        <v>2.1991</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4769</v>
+        <v>2.2363</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.3003</v>
       </c>
       <c r="K17" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="M17" t="n">
-        <v>2.4769</v>
+        <v>2.5366</v>
       </c>
       <c r="N17" t="n">
-        <v>209</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9304</v>
+        <v>2.0132</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8731</v>
+        <v>0.9106</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3585</v>
+        <v>0.3581</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9304</v>
+        <v>2.0132</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9304</v>
+        <v>0.6676</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.3456</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9304</v>
+        <v>0.6676</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9304</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.3456</v>
       </c>
       <c r="K18" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9304</v>
+        <v>2.0245</v>
       </c>
       <c r="N18" t="n">
-        <v>193</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7728</v>
+        <v>1.9304</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8018</v>
+        <v>0.8731</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2948</v>
+        <v>0.3252</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7728</v>
+        <v>1.9304</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4272</v>
+        <v>1.9304</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3456</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4272</v>
+        <v>1.9304</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4312</v>
+        <v>1.9304</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3456</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="L19" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7768</v>
+        <v>1.9304</v>
       </c>
       <c r="N19" t="n">
-        <v>418</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7634</v>
+        <v>1.8061</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7976</v>
+        <v>0.8169</v>
       </c>
       <c r="D20" t="n">
-        <v>0.291</v>
+        <v>0.2756</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7634</v>
+        <v>1.8061</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4154</v>
+        <v>2.4581</v>
       </c>
       <c r="G20" t="n">
         <v>-0.652</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4154</v>
+        <v>2.4581</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4154</v>
+        <v>2.4581</v>
       </c>
       <c r="J20" t="n">
         <v>-0.652</v>
@@ -1357,7 +1357,7 @@
         <v>56</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7634</v>
+        <v>1.8061</v>
       </c>
       <c r="N20" t="n">
         <v>223</v>
@@ -1366,35 +1366,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.7206</v>
+        <v>1.7859</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7782</v>
+        <v>0.8077</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2737</v>
+        <v>0.2676</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7206</v>
+        <v>1.7859</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1881</v>
+        <v>2.6108</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5325</v>
+        <v>-0.8249</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1881</v>
+        <v>2.6108</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1881</v>
+        <v>2.6108</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5325</v>
+        <v>-0.8249</v>
       </c>
       <c r="K21" t="n">
         <v>167</v>
@@ -1403,7 +1403,7 @@
         <v>56</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7206</v>
+        <v>1.7859</v>
       </c>
       <c r="N21" t="n">
         <v>223</v>
@@ -1412,35 +1412,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6368</v>
+        <v>1.7206</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7403</v>
+        <v>0.7782</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2399</v>
+        <v>0.2416</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6368</v>
+        <v>1.7206</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4617</v>
+        <v>1.1881</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8249</v>
+        <v>0.5325</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4617</v>
+        <v>1.1881</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4617</v>
+        <v>1.1881</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8249</v>
+        <v>0.5325</v>
       </c>
       <c r="K22" t="n">
         <v>167</v>
@@ -1449,7 +1449,7 @@
         <v>56</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6368</v>
+        <v>1.7206</v>
       </c>
       <c r="N22" t="n">
         <v>223</v>
@@ -1458,323 +1458,323 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NEOFRAG</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3284</v>
+        <v>1.3422</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6008</v>
+        <v>0.6071</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1153</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3284</v>
+        <v>1.3422</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3284</v>
+        <v>1.3422</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3284</v>
+        <v>1.3422</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3346</v>
+        <v>1.3422</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>217</v>
+        <v>132</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3346</v>
+        <v>1.3422</v>
       </c>
       <c r="N23" t="n">
-        <v>217</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>NEOFRAG</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2422</v>
+        <v>1.3234</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5618</v>
+        <v>0.5986</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0805</v>
+        <v>0.0833</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2422</v>
+        <v>1.3234</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2422</v>
+        <v>1.3234</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2422</v>
+        <v>1.3234</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2422</v>
+        <v>1.3346</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2422</v>
+        <v>1.3346</v>
       </c>
       <c r="N24" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1575</v>
+        <v>1.2422</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5235</v>
+        <v>0.5618</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0462</v>
+        <v>0.051</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1575</v>
+        <v>1.2422</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9101</v>
+        <v>1.2422</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2474</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9101</v>
+        <v>1.2422</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7377</v>
+        <v>1.2422</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2474</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L25" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9851000000000001</v>
+        <v>1.2422</v>
       </c>
       <c r="N25" t="n">
-        <v>218</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.0646</v>
+        <v>1.1606</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4815</v>
+        <v>0.5249</v>
       </c>
       <c r="D26" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0185</v>
       </c>
       <c r="E26" t="n">
-        <v>1.0646</v>
+        <v>1.1606</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0646</v>
+        <v>0.9132</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.2474</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0646</v>
+        <v>0.9132</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0696</v>
+        <v>0.7402</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.2474</v>
       </c>
       <c r="K26" t="n">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0696</v>
+        <v>0.9876</v>
       </c>
       <c r="N26" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.0546</v>
+        <v>1.0606</v>
       </c>
       <c r="C27" t="n">
-        <v>0.477</v>
+        <v>0.4797</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0047</v>
+        <v>-0.0214</v>
       </c>
       <c r="E27" t="n">
-        <v>1.0546</v>
+        <v>1.0606</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0546</v>
+        <v>1.0606</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0546</v>
+        <v>1.0606</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0546</v>
+        <v>1.0696</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.0546</v>
+        <v>1.0696</v>
       </c>
       <c r="N27" t="n">
-        <v>100</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.0047</v>
+        <v>1.0546</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4544</v>
+        <v>0.477</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0155</v>
+        <v>-0.0238</v>
       </c>
       <c r="E28" t="n">
-        <v>1.0047</v>
+        <v>1.0546</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0047</v>
+        <v>1.0546</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0047</v>
+        <v>1.0546</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0047</v>
+        <v>1.0546</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.0047</v>
+        <v>1.0546</v>
       </c>
       <c r="N28" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9056</v>
+        <v>1.0353</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4096</v>
+        <v>0.4683</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0555</v>
+        <v>-0.0314</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9056</v>
+        <v>1.0353</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9056</v>
+        <v>1.3473</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.312</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9056</v>
+        <v>1.3473</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9056</v>
+        <v>1.3473</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.312</v>
       </c>
       <c r="K29" t="n">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9056</v>
+        <v>1.0353</v>
       </c>
       <c r="N29" t="n">
-        <v>132</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.74</v>
+        <v>1.0308</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3347</v>
+        <v>0.4662</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1224</v>
+        <v>-0.0332</v>
       </c>
       <c r="E30" t="n">
-        <v>0.74</v>
+        <v>1.0308</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6503</v>
+        <v>0.9411</v>
       </c>
       <c r="G30" t="n">
         <v>0.0897</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6503</v>
+        <v>0.9411</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5271</v>
+        <v>0.7628</v>
       </c>
       <c r="J30" t="n">
         <v>0.0897</v>
@@ -1817,7 +1817,7 @@
         <v>82</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6168</v>
+        <v>0.8525</v>
       </c>
       <c r="N30" t="n">
         <v>255</v>
@@ -1826,952 +1826,952 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7361</v>
+        <v>1.0047</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3329</v>
+        <v>0.4544</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.124</v>
+        <v>-0.0436</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7361</v>
+        <v>1.0047</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7361</v>
+        <v>1.0047</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7361</v>
+        <v>1.0047</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7361</v>
+        <v>1.0047</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7361</v>
+        <v>1.0047</v>
       </c>
       <c r="N31" t="n">
-        <v>193</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Annihilation</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6957</v>
+        <v>0.7822</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3147</v>
+        <v>0.3538</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1403</v>
+        <v>-0.1323</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6957</v>
+        <v>0.7822</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6957</v>
+        <v>1.0612</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.279</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6957</v>
+        <v>1.0612</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6957</v>
+        <v>0.8601</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.279</v>
       </c>
       <c r="K32" t="n">
         <v>173</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6957</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>173</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6758</v>
+        <v>0.7361</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3057</v>
+        <v>0.3329</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1484</v>
+        <v>-0.1506</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6758</v>
+        <v>0.7361</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6758</v>
+        <v>0.7361</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6758</v>
+        <v>0.7361</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6758</v>
+        <v>0.7361</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6758</v>
+        <v>0.7361</v>
       </c>
       <c r="N33" t="n">
-        <v>100</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Annihilation</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5814</v>
+        <v>0.6957</v>
       </c>
       <c r="C34" t="n">
-        <v>0.263</v>
+        <v>0.3147</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1865</v>
+        <v>-0.1667</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5814</v>
+        <v>0.6957</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5814</v>
+        <v>0.6957</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5814</v>
+        <v>0.6957</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5814</v>
+        <v>0.6957</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5814</v>
+        <v>0.6957</v>
       </c>
       <c r="N34" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>F1KU</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5803</v>
+        <v>0.6758</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2625</v>
+        <v>0.3057</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1869</v>
+        <v>-0.1747</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5803</v>
+        <v>0.6758</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5803</v>
+        <v>0.6758</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5803</v>
+        <v>0.6758</v>
       </c>
       <c r="I35" t="n">
-        <v>0.583</v>
+        <v>0.6758</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>217</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.583</v>
+        <v>0.6758</v>
       </c>
       <c r="N35" t="n">
-        <v>217</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5743</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2598</v>
+        <v>0.2929</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1894</v>
+        <v>-0.1859</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5743</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5743</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5743</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5743</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5743</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4914</v>
+        <v>0.5814</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2223</v>
+        <v>0.263</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2228</v>
+        <v>-0.2123</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4914</v>
+        <v>0.5814</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7704</v>
+        <v>0.5814</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.279</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7704</v>
+        <v>0.5814</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6244</v>
+        <v>0.5814</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.279</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="L37" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3453999999999999</v>
+        <v>0.5814</v>
       </c>
       <c r="N37" t="n">
-        <v>255</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>F1KU</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4821</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>0.218</v>
+        <v>0.2615</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2266</v>
+        <v>-0.2136</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4821</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7941</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.312</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7941</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7941</v>
+        <v>0.583</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.312</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="L38" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4821</v>
+        <v>0.583</v>
       </c>
       <c r="N38" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3621</v>
+        <v>0.5743</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1638</v>
+        <v>0.2598</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2751</v>
+        <v>-0.2151</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3621</v>
+        <v>0.5743</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3621</v>
+        <v>0.5743</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3621</v>
+        <v>0.5743</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3621</v>
+        <v>0.5743</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3621</v>
+        <v>0.5743</v>
       </c>
       <c r="N39" t="n">
-        <v>132</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3234</v>
+        <v>0.3621</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1463</v>
+        <v>0.1638</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2907</v>
+        <v>-0.2996</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3234</v>
+        <v>0.3621</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3234</v>
+        <v>0.3621</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3234</v>
+        <v>0.3621</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3234</v>
+        <v>0.3621</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3234</v>
+        <v>0.3621</v>
       </c>
       <c r="N40" t="n">
-        <v>100</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3169</v>
+        <v>0.3234</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1433</v>
+        <v>0.1463</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2933</v>
+        <v>-0.3151</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3169</v>
+        <v>0.3234</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3169</v>
+        <v>0.3234</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3169</v>
+        <v>0.3234</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3169</v>
+        <v>0.3234</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>209</v>
+        <v>100</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3169</v>
+        <v>0.3234</v>
       </c>
       <c r="N41" t="n">
-        <v>209</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2748</v>
+        <v>0.3169</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1243</v>
+        <v>0.1433</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3103</v>
+        <v>-0.3177</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2748</v>
+        <v>0.3169</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3584</v>
+        <v>0.3169</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.08359999999999999</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3584</v>
+        <v>0.3169</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3601</v>
+        <v>0.3169</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.08359999999999999</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="L42" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2765</v>
+        <v>0.3169</v>
       </c>
       <c r="N42" t="n">
-        <v>261</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.188</v>
+        <v>0.2735</v>
       </c>
       <c r="C43" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1237</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3454</v>
+        <v>-0.3349</v>
       </c>
       <c r="E43" t="n">
-        <v>0.188</v>
+        <v>0.2735</v>
       </c>
       <c r="F43" t="n">
-        <v>0.188</v>
+        <v>0.3571</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0.188</v>
+        <v>0.3571</v>
       </c>
       <c r="I43" t="n">
-        <v>0.188</v>
+        <v>0.3601</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M43" t="n">
-        <v>0.188</v>
+        <v>0.2765</v>
       </c>
       <c r="N43" t="n">
-        <v>42</v>
+        <v>261</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JOTA</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1853</v>
+        <v>0.188</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0838</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3465</v>
+        <v>-0.369</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1853</v>
+        <v>0.188</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1853</v>
+        <v>0.188</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1853</v>
+        <v>0.188</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1853</v>
+        <v>0.188</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1853</v>
+        <v>0.188</v>
       </c>
       <c r="N44" t="n">
-        <v>98</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>JOTA</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1517</v>
+        <v>0.1853</v>
       </c>
       <c r="C45" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0838</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3601</v>
+        <v>-0.3701</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1517</v>
+        <v>0.1853</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1517</v>
+        <v>0.1853</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1517</v>
+        <v>0.1853</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1517</v>
+        <v>0.1853</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1517</v>
+        <v>0.1853</v>
       </c>
       <c r="N45" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0917</v>
+        <v>0.1768</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0415</v>
+        <v>0.08</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3843</v>
+        <v>-0.3735</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0917</v>
+        <v>0.1768</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0917</v>
+        <v>0.5108</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.334</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0917</v>
+        <v>0.5108</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0917</v>
+        <v>0.5151</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.334</v>
       </c>
       <c r="K46" t="n">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0917</v>
+        <v>0.1811</v>
       </c>
       <c r="N46" t="n">
-        <v>98</v>
+        <v>261</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0717</v>
+        <v>0.1517</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0324</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3924</v>
+        <v>-0.3835</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0717</v>
+        <v>0.1517</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0717</v>
+        <v>0.1517</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0717</v>
+        <v>0.1517</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0717</v>
+        <v>0.1517</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0717</v>
+        <v>0.1517</v>
       </c>
       <c r="N47" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0066</v>
+        <v>0.0917</v>
       </c>
       <c r="C48" t="n">
-        <v>0.003</v>
+        <v>0.0415</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4187</v>
+        <v>-0.4074</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0066</v>
+        <v>0.0917</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3406</v>
+        <v>0.0917</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.334</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3406</v>
+        <v>0.0917</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3422</v>
+        <v>0.0917</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.334</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>176</v>
+        <v>98</v>
       </c>
       <c r="L48" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.008199999999999985</v>
+        <v>0.0917</v>
       </c>
       <c r="N48" t="n">
-        <v>261</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1694</v>
+        <v>0.0717</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0766</v>
+        <v>0.0324</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4898</v>
+        <v>-0.4153</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1694</v>
+        <v>0.0717</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8306</v>
+        <v>0.0717</v>
       </c>
       <c r="G49" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8306</v>
+        <v>0.0717</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8345</v>
+        <v>0.0717</v>
       </c>
       <c r="J49" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="L49" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1655</v>
+        <v>0.0717</v>
       </c>
       <c r="N49" t="n">
-        <v>261</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1822</v>
+        <v>-0.0003</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0824</v>
+        <v>-0.0001</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.495</v>
+        <v>-0.444</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1822</v>
+        <v>-0.0003</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1822</v>
+        <v>-0.0003</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1822</v>
+        <v>-0.0003</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1822</v>
+        <v>-0.0003</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>91</v>
+        <v>209</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1822</v>
+        <v>-0.0003</v>
       </c>
       <c r="N50" t="n">
-        <v>91</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2689</v>
+        <v>-0.0566</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1216</v>
+        <v>-0.0256</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.53</v>
+        <v>-0.4665</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.2689</v>
+        <v>-0.0566</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2689</v>
+        <v>-0.0566</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2689</v>
+        <v>-0.0566</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2689</v>
+        <v>-0.0566</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.2689</v>
+        <v>-0.0566</v>
       </c>
       <c r="N51" t="n">
         <v>132</v>
@@ -2792,645 +2792,645 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.271</v>
+        <v>-0.1725</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1226</v>
+        <v>-0.078</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5308</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.271</v>
+        <v>-0.1725</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.271</v>
+        <v>0.8275</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.271</v>
+        <v>0.8275</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.271</v>
+        <v>0.8345</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K52" t="n">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.271</v>
+        <v>-0.1655</v>
       </c>
       <c r="N52" t="n">
-        <v>75</v>
+        <v>261</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3239</v>
+        <v>-0.1822</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1465</v>
+        <v>-0.0824</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5522</v>
+        <v>-0.5165</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3239</v>
+        <v>-0.1822</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3239</v>
+        <v>-0.1822</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3239</v>
+        <v>-0.1822</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3239</v>
+        <v>-0.1822</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3239</v>
+        <v>-0.1822</v>
       </c>
       <c r="N53" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3325</v>
+        <v>-0.271</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1504</v>
+        <v>-0.1226</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5557</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3325</v>
+        <v>-0.271</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3325</v>
+        <v>-0.271</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3325</v>
+        <v>-0.271</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3325</v>
+        <v>-0.271</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3325</v>
+        <v>-0.271</v>
       </c>
       <c r="N54" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>mynio</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3751</v>
+        <v>-0.3239</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1697</v>
+        <v>-0.1465</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5729</v>
+        <v>-0.573</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3751</v>
+        <v>-0.3239</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3751</v>
+        <v>-0.3239</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3751</v>
+        <v>-0.3239</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3751</v>
+        <v>-0.3239</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3751</v>
+        <v>-0.3239</v>
       </c>
       <c r="N55" t="n">
-        <v>193</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4281</v>
+        <v>-0.3325</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1936</v>
+        <v>-0.1504</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.5764</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4281</v>
+        <v>-0.3325</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4096</v>
+        <v>-0.3325</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.8377</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4096</v>
+        <v>-0.3325</v>
       </c>
       <c r="I56" t="n">
-        <v>0.332</v>
+        <v>-0.3325</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.8377</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>173</v>
+        <v>98</v>
       </c>
       <c r="L56" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.5057</v>
+        <v>-0.3325</v>
       </c>
       <c r="N56" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>hyped</t>
+          <t>mynio</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.5321</v>
+        <v>-0.3751</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2407</v>
+        <v>-0.1697</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6363</v>
+        <v>-0.5934</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5321</v>
+        <v>-0.3751</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.715</v>
+        <v>-0.3751</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1829</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.715</v>
+        <v>-0.3751</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.715</v>
+        <v>-0.3751</v>
       </c>
       <c r="J57" t="n">
-        <v>0.1829</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="L57" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.5321</v>
+        <v>-0.3751</v>
       </c>
       <c r="N57" t="n">
-        <v>223</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5462</v>
+        <v>-0.4281</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.247</v>
+        <v>-0.1936</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.642</v>
+        <v>-0.6145</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5462</v>
+        <v>-0.4281</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5462</v>
+        <v>0.4096</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-0.8377</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5462</v>
+        <v>0.4096</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5462</v>
+        <v>0.332</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-0.8377</v>
       </c>
       <c r="K58" t="n">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.5462</v>
+        <v>-0.5057</v>
       </c>
       <c r="N58" t="n">
-        <v>132</v>
+        <v>255</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FASHR</t>
+          <t>hyped</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6458</v>
+        <v>-0.4485</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2921</v>
+        <v>-0.2029</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6823</v>
+        <v>-0.6226</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6458</v>
+        <v>-0.4485</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.6458</v>
+        <v>-0.6314</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.1829</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.6458</v>
+        <v>-0.6314</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.6458</v>
+        <v>-0.6314</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>0.1829</v>
       </c>
       <c r="K59" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.6458</v>
+        <v>-0.4485</v>
       </c>
       <c r="N59" t="n">
-        <v>149</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kylar</t>
+          <t>FASHR</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6698</v>
+        <v>-0.6458</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3029</v>
+        <v>-0.2921</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6919</v>
+        <v>-0.7012</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6698</v>
+        <v>-0.6458</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.6698</v>
+        <v>-0.6458</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.6698</v>
+        <v>-0.6458</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6698</v>
+        <v>-0.6458</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.6698</v>
+        <v>-0.6458</v>
       </c>
       <c r="N60" t="n">
-        <v>193</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Kylar</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.7054</v>
+        <v>-0.6698</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.319</v>
+        <v>-0.3029</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7063</v>
+        <v>-0.7108</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.7054</v>
+        <v>-0.6698</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7054</v>
+        <v>-0.6698</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7054</v>
+        <v>-0.6698</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7054</v>
+        <v>-0.6698</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.7054</v>
+        <v>-0.6698</v>
       </c>
       <c r="N61" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.7054</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3335</v>
+        <v>-0.319</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.7249</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.7054</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.7054</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.7054</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7408</v>
+        <v>-0.7054</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7408</v>
+        <v>-0.7054</v>
       </c>
       <c r="N62" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7548</v>
+        <v>-0.7346</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3414</v>
+        <v>-0.3323</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.7366</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7548</v>
+        <v>-0.7346</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7548</v>
+        <v>-0.7346</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.7548</v>
+        <v>-0.7346</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.7548</v>
+        <v>-0.7408</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.7548</v>
+        <v>-0.7408</v>
       </c>
       <c r="N63" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.785</v>
+        <v>-0.7548</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.355</v>
+        <v>-0.3414</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7385</v>
+        <v>-0.7446</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.785</v>
+        <v>-0.7548</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6554</v>
+        <v>-0.7548</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.1296</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6554</v>
+        <v>-0.7548</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6615</v>
+        <v>-0.7548</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.1296</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>224</v>
+        <v>149</v>
       </c>
       <c r="L64" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7910999999999999</v>
+        <v>-0.7548</v>
       </c>
       <c r="N64" t="n">
-        <v>438</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.7801</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.36</v>
+        <v>-0.3528</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7429</v>
+        <v>-0.7547</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.7801</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.6505</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>-0.1296</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.6505</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.6615</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>-0.1296</v>
       </c>
       <c r="K65" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.7910999999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>209</v>
+        <v>438</v>
       </c>
     </row>
     <row r="66">
@@ -3446,7 +3446,7 @@
         <v>-0.3618</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="E66" t="n">
         <v>-0.7999000000000001</v>
@@ -3492,7 +3492,7 @@
         <v>-0.376</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7572</v>
+        <v>-0.7751</v>
       </c>
       <c r="E67" t="n">
         <v>-0.8314</v>
@@ -3538,7 +3538,7 @@
         <v>-0.392</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7715</v>
+        <v>-0.7892</v>
       </c>
       <c r="E68" t="n">
         <v>-0.8667</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9275</v>
+        <v>-0.8875</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4195</v>
+        <v>-0.4014</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7961</v>
+        <v>-0.7975</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9275</v>
+        <v>-0.8875</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9275</v>
+        <v>-0.8875</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.9275</v>
+        <v>-0.8875</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.9361</v>
+        <v>-0.9025</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.9361</v>
+        <v>-0.9025</v>
       </c>
       <c r="N69" t="n">
         <v>224</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0309</v>
+        <v>-1.0232</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4663</v>
+        <v>-0.4628</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8378</v>
+        <v>-0.8516</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0309</v>
+        <v>-1.0232</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.0309</v>
+        <v>-1.0232</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.0309</v>
+        <v>-1.0232</v>
       </c>
       <c r="I70" t="n">
         <v>-1.0405</v>
@@ -3676,7 +3676,7 @@
         <v>-0.547</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.91</v>
+        <v>-0.9258</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2095</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5804</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9397</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2832</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5956</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9533</v>
+        <v>-0.9685</v>
       </c>
       <c r="E73" t="n">
         <v>-1.3168</v>
@@ -3814,7 +3814,7 @@
         <v>-0.6535</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0051</v>
+        <v>-1.0196</v>
       </c>
       <c r="E74" t="n">
         <v>-1.4449</v>
@@ -3860,7 +3860,7 @@
         <v>-0.6942</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0414</v>
+        <v>-1.0554</v>
       </c>
       <c r="E75" t="n">
         <v>-1.5348</v>
@@ -3906,7 +3906,7 @@
         <v>-0.7002</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0468</v>
+        <v>-1.0607</v>
       </c>
       <c r="E76" t="n">
         <v>-1.5481</v>
@@ -3952,7 +3952,7 @@
         <v>-0.787</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1243</v>
+        <v>-1.1372</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7401</v>
@@ -3998,7 +3998,7 @@
         <v>-0.8343</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1665</v>
+        <v>-1.1788</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8445</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.4349</v>
+        <v>-2.4272</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.1013</v>
+        <v>-1.0978</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.405</v>
+        <v>-1.4109</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.4349</v>
+        <v>-2.4272</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.6855</v>
+        <v>-0.6778</v>
       </c>
       <c r="G79" t="n">
         <v>-1.7494</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.6855</v>
+        <v>-0.6778</v>
       </c>
       <c r="I79" t="n">
         <v>-0.6951000000000001</v>
@@ -4090,7 +4090,7 @@
         <v>-1.3879</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.661</v>
+        <v>-1.6664</v>
       </c>
       <c r="E80" t="n">
         <v>-3.0685</v>
@@ -4136,7 +4136,7 @@
         <v>-1.7031</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.9425</v>
+        <v>-1.9441</v>
       </c>
       <c r="E81" t="n">
         <v>-3.7655</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.9504</v>
+        <v>-3.9357</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.7867</v>
+        <v>-1.7801</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.0172</v>
+        <v>-2.0119</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.9504</v>
+        <v>-3.9357</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.9504</v>
+        <v>-3.9357</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-3.9504</v>
+        <v>-3.9357</v>
       </c>
       <c r="I82" t="n">
         <v>-3.9688</v>
